--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99039</v>
+        <v>99040</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99039</v>
+        <v>99040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99039</v>
+        <v>99040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99039</v>
+        <v>99040</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129406095</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>129403984</v>
       </c>
       <c r="B14" t="n">
-        <v>99039</v>
+        <v>99040</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>129404650</v>
       </c>
       <c r="B15" t="n">
-        <v>99039</v>
+        <v>99040</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>129405597</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99040</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>129405968</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>129404168</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99040</v>
+        <v>99044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129406329</v>
       </c>
       <c r="B8" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129405887</v>
+        <v>129405463</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,42 +1583,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494440</v>
+        <v>494466</v>
       </c>
       <c r="R9" t="n">
-        <v>7004634</v>
+        <v>7004694</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,7 +1642,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1657,7 +1652,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,12 +1681,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1709,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129405463</v>
+        <v>129405887</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,37 +1715,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494466</v>
+        <v>494440</v>
       </c>
       <c r="R10" t="n">
-        <v>7004694</v>
+        <v>7004634</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99040</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99040</v>
+        <v>99044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129406095</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>129403984</v>
       </c>
       <c r="B14" t="n">
-        <v>99040</v>
+        <v>99044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>129404650</v>
       </c>
       <c r="B15" t="n">
-        <v>99040</v>
+        <v>99044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>129405597</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129405408</v>
       </c>
       <c r="B19" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129405463</v>
+        <v>129405887</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>91543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,37 +1583,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494466</v>
+        <v>494440</v>
       </c>
       <c r="R9" t="n">
-        <v>7004694</v>
+        <v>7004634</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1642,7 +1647,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1652,7 +1657,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1681,12 +1686,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1704,10 +1709,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129405887</v>
+        <v>129405463</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,42 +1720,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494440</v>
+        <v>494466</v>
       </c>
       <c r="R10" t="n">
-        <v>7004634</v>
+        <v>7004694</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>99046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>129405968</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>129404168</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99044</v>
+        <v>99046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129406329</v>
       </c>
       <c r="B8" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129405887</v>
+        <v>129405463</v>
       </c>
       <c r="B9" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,42 +1583,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494440</v>
+        <v>494466</v>
       </c>
       <c r="R9" t="n">
-        <v>7004634</v>
+        <v>7004694</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,7 +1642,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1657,7 +1652,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,12 +1681,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1709,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129405463</v>
+        <v>129405887</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,37 +1715,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494466</v>
+        <v>494440</v>
       </c>
       <c r="R10" t="n">
-        <v>7004694</v>
+        <v>7004634</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99044</v>
+        <v>99046</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99044</v>
+        <v>99046</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129406095</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>129403984</v>
       </c>
       <c r="B14" t="n">
-        <v>99044</v>
+        <v>99046</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2328,38 +2328,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129404650</v>
+        <v>129405597</v>
       </c>
       <c r="B15" t="n">
-        <v>99044</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bladfällning, vissnar</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2368,13 +2382,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494503</v>
+        <v>494407</v>
       </c>
       <c r="R15" t="n">
-        <v>7004768</v>
+        <v>7004705</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2403,7 +2417,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2413,7 +2427,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2427,7 +2446,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2445,52 +2464,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129405597</v>
+        <v>129404650</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>99046</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>bladfällning, vissnar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2499,13 +2504,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494407</v>
+        <v>494503</v>
       </c>
       <c r="R16" t="n">
-        <v>7004705</v>
+        <v>7004768</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2534,7 +2539,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2544,12 +2549,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129405408</v>
       </c>
       <c r="B19" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99046</v>
+        <v>99050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99046</v>
+        <v>99050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129406329</v>
       </c>
       <c r="B8" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129405463</v>
+        <v>129405887</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,37 +1583,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494466</v>
+        <v>494440</v>
       </c>
       <c r="R9" t="n">
-        <v>7004694</v>
+        <v>7004634</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1642,7 +1647,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1652,7 +1657,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1681,12 +1686,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1704,10 +1709,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129405887</v>
+        <v>129405463</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,42 +1720,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494440</v>
+        <v>494466</v>
       </c>
       <c r="R10" t="n">
-        <v>7004634</v>
+        <v>7004694</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99046</v>
+        <v>99050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99046</v>
+        <v>99050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,67 +2075,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406095</v>
+        <v>129403984</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>99050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
+          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494525</v>
+        <v>494565</v>
       </c>
       <c r="R13" t="n">
-        <v>7004569</v>
+        <v>7004899</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2164,7 +2150,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2174,12 +2160,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2211,53 +2192,67 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129403984</v>
+        <v>129406095</v>
       </c>
       <c r="B14" t="n">
-        <v>99046</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
+          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494565</v>
+        <v>494525</v>
       </c>
       <c r="R14" t="n">
-        <v>7004899</v>
+        <v>7004569</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2286,7 +2281,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2296,7 +2291,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,52 +2328,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129405597</v>
+        <v>129404650</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>99050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>bladfällning, vissnar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2382,13 +2368,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494407</v>
+        <v>494503</v>
       </c>
       <c r="R15" t="n">
-        <v>7004705</v>
+        <v>7004768</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2417,7 +2403,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2427,12 +2413,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2446,7 +2427,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2464,38 +2445,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129404650</v>
+        <v>129405597</v>
       </c>
       <c r="B16" t="n">
-        <v>99046</v>
+        <v>98716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>bladfällning, vissnar</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2504,13 +2499,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494503</v>
+        <v>494407</v>
       </c>
       <c r="R16" t="n">
-        <v>7004768</v>
+        <v>7004705</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2539,7 +2534,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2549,7 +2544,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129405408</v>
       </c>
       <c r="B19" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99050</v>
+        <v>99058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99050</v>
+        <v>99058</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129406329</v>
       </c>
       <c r="B8" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>129405887</v>
       </c>
       <c r="B9" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99050</v>
+        <v>99058</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99050</v>
+        <v>99058</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129403984</v>
       </c>
       <c r="B13" t="n">
-        <v>99050</v>
+        <v>99058</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129406095</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2328,38 +2328,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129404650</v>
+        <v>129405597</v>
       </c>
       <c r="B15" t="n">
-        <v>99050</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bladfällning, vissnar</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2368,13 +2382,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494503</v>
+        <v>494407</v>
       </c>
       <c r="R15" t="n">
-        <v>7004768</v>
+        <v>7004705</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2403,7 +2417,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2413,7 +2427,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2427,7 +2446,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2445,52 +2464,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129405597</v>
+        <v>129404650</v>
       </c>
       <c r="B16" t="n">
-        <v>98716</v>
+        <v>99058</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>bladfällning, vissnar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2499,13 +2504,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494407</v>
+        <v>494503</v>
       </c>
       <c r="R16" t="n">
-        <v>7004705</v>
+        <v>7004768</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2534,7 +2539,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2544,12 +2549,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129405408</v>
       </c>
       <c r="B19" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129405887</v>
+        <v>129405463</v>
       </c>
       <c r="B9" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,42 +1583,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494440</v>
+        <v>494466</v>
       </c>
       <c r="R9" t="n">
-        <v>7004634</v>
+        <v>7004694</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,7 +1642,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1657,7 +1652,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,12 +1681,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1709,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129405463</v>
+        <v>129405887</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,37 +1715,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494466</v>
+        <v>494440</v>
       </c>
       <c r="R10" t="n">
-        <v>7004694</v>
+        <v>7004634</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2328,52 +2328,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129405597</v>
+        <v>129404650</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>99058</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>bladfällning, vissnar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2382,13 +2368,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494407</v>
+        <v>494503</v>
       </c>
       <c r="R15" t="n">
-        <v>7004705</v>
+        <v>7004768</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2417,7 +2403,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2427,12 +2413,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2446,7 +2427,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2464,38 +2445,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129404650</v>
+        <v>129405597</v>
       </c>
       <c r="B16" t="n">
-        <v>99058</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>bladfällning, vissnar</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2504,13 +2499,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494503</v>
+        <v>494407</v>
       </c>
       <c r="R16" t="n">
-        <v>7004768</v>
+        <v>7004705</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2539,7 +2534,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2549,7 +2544,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99058</v>
+        <v>99061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99058</v>
+        <v>99061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129406329</v>
       </c>
       <c r="B8" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129405887</v>
       </c>
       <c r="B10" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99058</v>
+        <v>99061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99058</v>
+        <v>99061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129403984</v>
       </c>
       <c r="B13" t="n">
-        <v>99058</v>
+        <v>99061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129406095</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>129404650</v>
       </c>
       <c r="B15" t="n">
-        <v>99058</v>
+        <v>99061</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>129405597</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129405408</v>
       </c>
       <c r="B19" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129405463</v>
+        <v>129405887</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,37 +1583,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494466</v>
+        <v>494440</v>
       </c>
       <c r="R9" t="n">
-        <v>7004694</v>
+        <v>7004634</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1642,7 +1647,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1652,7 +1657,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1681,12 +1686,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1704,10 +1709,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129405887</v>
+        <v>129405463</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,42 +1720,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494440</v>
+        <v>494466</v>
       </c>
       <c r="R10" t="n">
-        <v>7004634</v>
+        <v>7004694</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2075,53 +2075,67 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129403984</v>
+        <v>129406095</v>
       </c>
       <c r="B13" t="n">
-        <v>99061</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
+          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494565</v>
+        <v>494525</v>
       </c>
       <c r="R13" t="n">
-        <v>7004899</v>
+        <v>7004569</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2150,7 +2164,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2160,7 +2174,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,67 +2211,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129406095</v>
+        <v>129403984</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>99061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
+          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494525</v>
+        <v>494565</v>
       </c>
       <c r="R14" t="n">
-        <v>7004569</v>
+        <v>7004899</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2281,7 +2286,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2291,12 +2296,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,38 +2328,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129404650</v>
+        <v>129405597</v>
       </c>
       <c r="B15" t="n">
-        <v>99061</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bladfällning, vissnar</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2368,13 +2382,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494503</v>
+        <v>494407</v>
       </c>
       <c r="R15" t="n">
-        <v>7004768</v>
+        <v>7004705</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2403,7 +2417,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2413,7 +2427,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2427,7 +2446,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2445,52 +2464,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129405597</v>
+        <v>129404650</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>99061</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>bladfällning, vissnar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2499,13 +2504,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494407</v>
+        <v>494503</v>
       </c>
       <c r="R16" t="n">
-        <v>7004705</v>
+        <v>7004768</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2534,7 +2539,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2544,12 +2549,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -2328,52 +2328,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129405597</v>
+        <v>129404650</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>99061</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>bladfällning, vissnar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2382,13 +2368,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494407</v>
+        <v>494503</v>
       </c>
       <c r="R15" t="n">
-        <v>7004705</v>
+        <v>7004768</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2417,7 +2403,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2427,12 +2413,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2446,7 +2427,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2464,38 +2445,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129404650</v>
+        <v>129405597</v>
       </c>
       <c r="B16" t="n">
-        <v>99061</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>bladfällning, vissnar</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2504,13 +2499,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494503</v>
+        <v>494407</v>
       </c>
       <c r="R16" t="n">
-        <v>7004768</v>
+        <v>7004705</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2539,7 +2534,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2549,7 +2544,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129405887</v>
+        <v>129405463</v>
       </c>
       <c r="B9" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,42 +1583,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494440</v>
+        <v>494466</v>
       </c>
       <c r="R9" t="n">
-        <v>7004634</v>
+        <v>7004694</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,7 +1642,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1657,7 +1652,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,12 +1681,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1709,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129405463</v>
+        <v>129405887</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,37 +1715,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494466</v>
+        <v>494440</v>
       </c>
       <c r="R10" t="n">
-        <v>7004694</v>
+        <v>7004634</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2075,67 +2075,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406095</v>
+        <v>129403984</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>99061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
+          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494525</v>
+        <v>494565</v>
       </c>
       <c r="R13" t="n">
-        <v>7004569</v>
+        <v>7004899</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2164,7 +2150,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2174,12 +2160,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2211,53 +2192,67 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129403984</v>
+        <v>129406095</v>
       </c>
       <c r="B14" t="n">
-        <v>99061</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
+          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494565</v>
+        <v>494525</v>
       </c>
       <c r="R14" t="n">
-        <v>7004899</v>
+        <v>7004569</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2286,7 +2281,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2296,7 +2291,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99061</v>
+        <v>99090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>129405968</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>129404168</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99061</v>
+        <v>99090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129406329</v>
       </c>
       <c r="B8" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>129405463</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129405887</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99061</v>
+        <v>99090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99061</v>
+        <v>99090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129403984</v>
       </c>
       <c r="B13" t="n">
-        <v>99061</v>
+        <v>99090</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129406095</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>129404650</v>
       </c>
       <c r="B15" t="n">
-        <v>99061</v>
+        <v>99090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>129405597</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>129404274</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129405408</v>
       </c>
       <c r="B19" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -2075,53 +2075,67 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129403984</v>
+        <v>129406095</v>
       </c>
       <c r="B13" t="n">
-        <v>99090</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
+          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494565</v>
+        <v>494525</v>
       </c>
       <c r="R13" t="n">
-        <v>7004899</v>
+        <v>7004569</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2150,7 +2164,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2160,7 +2174,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,67 +2211,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129406095</v>
+        <v>129403984</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>99090</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
+          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494525</v>
+        <v>494565</v>
       </c>
       <c r="R14" t="n">
-        <v>7004569</v>
+        <v>7004899</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2281,7 +2286,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2291,12 +2296,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,38 +2328,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129404650</v>
+        <v>129405597</v>
       </c>
       <c r="B15" t="n">
-        <v>99090</v>
+        <v>98756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bladfällning, vissnar</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2368,13 +2382,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494503</v>
+        <v>494407</v>
       </c>
       <c r="R15" t="n">
-        <v>7004768</v>
+        <v>7004705</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2403,7 +2417,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2413,7 +2427,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2427,7 +2446,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2445,52 +2464,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129405597</v>
+        <v>129404650</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>99090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>bladfällning, vissnar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2499,13 +2504,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494407</v>
+        <v>494503</v>
       </c>
       <c r="R16" t="n">
-        <v>7004705</v>
+        <v>7004768</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2534,7 +2539,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2544,12 +2549,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99090</v>
+        <v>99102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>129405968</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>129404168</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99090</v>
+        <v>99102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129406329</v>
       </c>
       <c r="B8" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>129405463</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129405887</v>
       </c>
       <c r="B10" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99090</v>
+        <v>99102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99090</v>
+        <v>99102</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,67 +2075,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406095</v>
+        <v>129403984</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>99102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
+          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494525</v>
+        <v>494565</v>
       </c>
       <c r="R13" t="n">
-        <v>7004569</v>
+        <v>7004899</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2164,7 +2150,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2174,12 +2160,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2211,53 +2192,67 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129403984</v>
+        <v>129406095</v>
       </c>
       <c r="B14" t="n">
-        <v>99090</v>
+        <v>98768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
+          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494565</v>
+        <v>494525</v>
       </c>
       <c r="R14" t="n">
-        <v>7004899</v>
+        <v>7004569</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2286,7 +2281,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2296,7 +2291,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2331,7 +2331,7 @@
         <v>129405597</v>
       </c>
       <c r="B15" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>129404650</v>
       </c>
       <c r="B16" t="n">
-        <v>99090</v>
+        <v>99102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>129404274</v>
       </c>
       <c r="B18" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129405408</v>
       </c>
       <c r="B19" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99102</v>
+        <v>99103</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>129405968</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>129404168</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99102</v>
+        <v>99103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129406329</v>
       </c>
       <c r="B8" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129405463</v>
+        <v>129405887</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,37 +1583,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494466</v>
+        <v>494440</v>
       </c>
       <c r="R9" t="n">
-        <v>7004694</v>
+        <v>7004634</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1642,7 +1647,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1652,7 +1657,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1681,12 +1686,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1704,10 +1709,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129405887</v>
+        <v>129405463</v>
       </c>
       <c r="B10" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,42 +1720,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494440</v>
+        <v>494466</v>
       </c>
       <c r="R10" t="n">
-        <v>7004634</v>
+        <v>7004694</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99102</v>
+        <v>99103</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99102</v>
+        <v>99103</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129403984</v>
       </c>
       <c r="B13" t="n">
-        <v>99102</v>
+        <v>99103</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129406095</v>
       </c>
       <c r="B14" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>129405597</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>129404650</v>
       </c>
       <c r="B16" t="n">
-        <v>99102</v>
+        <v>99103</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>129404274</v>
       </c>
       <c r="B18" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129405408</v>
       </c>
       <c r="B19" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99103</v>
+        <v>99108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>129405968</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>129404168</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99103</v>
+        <v>99108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129406329</v>
       </c>
       <c r="B8" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>129405887</v>
       </c>
       <c r="B9" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>129405463</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99103</v>
+        <v>99108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99103</v>
+        <v>99108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129403984</v>
       </c>
       <c r="B13" t="n">
-        <v>99103</v>
+        <v>99108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129406095</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>129405597</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>129404650</v>
       </c>
       <c r="B16" t="n">
-        <v>99103</v>
+        <v>99108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129405408</v>
       </c>
       <c r="B19" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -2075,53 +2075,67 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129403984</v>
+        <v>129406095</v>
       </c>
       <c r="B13" t="n">
-        <v>99108</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
+          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494565</v>
+        <v>494525</v>
       </c>
       <c r="R13" t="n">
-        <v>7004899</v>
+        <v>7004569</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2150,7 +2164,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2160,7 +2174,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,67 +2211,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129406095</v>
+        <v>129403984</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>99108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
+          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494525</v>
+        <v>494565</v>
       </c>
       <c r="R14" t="n">
-        <v>7004569</v>
+        <v>7004899</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2281,7 +2286,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2291,12 +2296,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,52 +2328,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129405597</v>
+        <v>129404650</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>99108</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>bladfällning, vissnar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2382,13 +2368,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494407</v>
+        <v>494503</v>
       </c>
       <c r="R15" t="n">
-        <v>7004705</v>
+        <v>7004768</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2417,7 +2403,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2427,12 +2413,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2446,7 +2427,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2464,38 +2445,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129404650</v>
+        <v>129405597</v>
       </c>
       <c r="B16" t="n">
-        <v>99108</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>bladfällning, vissnar</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2504,13 +2499,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494503</v>
+        <v>494407</v>
       </c>
       <c r="R16" t="n">
-        <v>7004768</v>
+        <v>7004705</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2539,7 +2534,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2549,7 +2544,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -2075,67 +2075,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406095</v>
+        <v>129403984</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>99108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
+          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494525</v>
+        <v>494565</v>
       </c>
       <c r="R13" t="n">
-        <v>7004569</v>
+        <v>7004899</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2164,7 +2150,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2174,12 +2160,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2211,53 +2192,67 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129403984</v>
+        <v>129406095</v>
       </c>
       <c r="B14" t="n">
-        <v>99108</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
+          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494565</v>
+        <v>494525</v>
       </c>
       <c r="R14" t="n">
-        <v>7004899</v>
+        <v>7004569</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2286,7 +2281,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2296,7 +2291,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99108</v>
+        <v>99112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99108</v>
+        <v>99112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129406329</v>
       </c>
       <c r="B8" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>129405887</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99108</v>
+        <v>99112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99108</v>
+        <v>99112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,53 +2075,67 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129403984</v>
+        <v>129406095</v>
       </c>
       <c r="B13" t="n">
-        <v>99108</v>
+        <v>98778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
+          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494565</v>
+        <v>494525</v>
       </c>
       <c r="R13" t="n">
-        <v>7004899</v>
+        <v>7004569</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2150,7 +2164,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2160,7 +2174,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,67 +2211,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129406095</v>
+        <v>129403984</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>99112</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
+          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494525</v>
+        <v>494565</v>
       </c>
       <c r="R14" t="n">
-        <v>7004569</v>
+        <v>7004899</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2281,7 +2286,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2291,12 +2296,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2331,7 +2331,7 @@
         <v>129404650</v>
       </c>
       <c r="B15" t="n">
-        <v>99108</v>
+        <v>99112</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>129405597</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129405408</v>
       </c>
       <c r="B19" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 44741-2025 artfynd.xlsx
+++ b/artfynd/A 44741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129406906</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>129403935</v>
       </c>
       <c r="B3" t="n">
-        <v>99112</v>
+        <v>99114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>129405358</v>
       </c>
       <c r="B6" t="n">
-        <v>99112</v>
+        <v>99114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>129405784</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129406329</v>
       </c>
       <c r="B8" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>129405887</v>
       </c>
       <c r="B9" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129404067</v>
       </c>
       <c r="B11" t="n">
-        <v>99112</v>
+        <v>99114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129403857</v>
       </c>
       <c r="B12" t="n">
-        <v>99112</v>
+        <v>99114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,67 +2075,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406095</v>
+        <v>129403984</v>
       </c>
       <c r="B13" t="n">
-        <v>98778</v>
+        <v>99114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
+          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494525</v>
+        <v>494565</v>
       </c>
       <c r="R13" t="n">
-        <v>7004569</v>
+        <v>7004899</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2164,7 +2150,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2174,12 +2160,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2211,53 +2192,67 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129403984</v>
+        <v>129406095</v>
       </c>
       <c r="B14" t="n">
-        <v>99112</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sotsvedbäcken, Sotsvedbäcken, Jmt</t>
+          <t>Malmdrolsmyren, Malmdrolsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494565</v>
+        <v>494525</v>
       </c>
       <c r="R14" t="n">
-        <v>7004899</v>
+        <v>7004569</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2286,7 +2281,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2296,7 +2291,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2331,7 +2331,7 @@
         <v>129404650</v>
       </c>
       <c r="B15" t="n">
-        <v>99112</v>
+        <v>99114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>129405597</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>129406284</v>
       </c>
       <c r="B17" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129405408</v>
       </c>
       <c r="B19" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
